--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2236-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2236-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0069AB6A-12E3-49FE-830B-14459BA791CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{93F68F7F-CE29-4774-9426-C7CAC2831A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{3E8499E7-F820-40AD-8F50-0736E526D562}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{7A85A1A0-1FA0-4592-AA43-07ED7E846437}"/>
   </bookViews>
   <sheets>
     <sheet name="2236-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1487,30 +1487,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{674A1C97-20BB-458C-92D8-955AE0EFD61D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA293EF-CF37-4018-A215-8A12DF047836}">
   <dimension ref="A1:X31"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="7" width="7.125" customWidth="1"/>
-    <col min="8" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.5" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="7" width="6.109375" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -1544,7 +1544,7 @@
       <c r="W1" s="29"/>
       <c r="X1" s="21"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
@@ -1580,7 +1580,7 @@
       <c r="W2" s="31"/>
       <c r="X2" s="32"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>2</v>
       </c>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="X3" s="35"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="24"/>
       <c r="B4" s="25"/>
       <c r="C4" s="7"/>
@@ -1700,7 +1700,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="36">
         <v>2025</v>
       </c>
@@ -1772,7 +1772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1846,7 +1846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="38">
         <v>2024</v>
       </c>
@@ -1918,7 +1918,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>29</v>
       </c>
@@ -1992,7 +1992,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2066,7 +2066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="36">
         <v>2023</v>
       </c>
@@ -2138,7 +2138,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>29</v>
       </c>
@@ -2212,7 +2212,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>29</v>
       </c>
@@ -2286,7 +2286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="38">
         <v>2022</v>
       </c>
@@ -2358,7 +2358,7 @@
         <v>1.26</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
@@ -2432,7 +2432,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2506,7 +2506,7 @@
         <v>0.91</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="36">
         <v>2021</v>
       </c>
@@ -2578,7 +2578,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>29</v>
       </c>
@@ -2652,7 +2652,7 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2726,7 +2726,7 @@
         <v>8.5399999999999991</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="38">
         <v>2020</v>
       </c>
@@ -2798,7 +2798,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
         <v>29</v>
       </c>
@@ -2872,7 +2872,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
         <v>29</v>
       </c>
@@ -2946,7 +2946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="36">
         <v>2019</v>
       </c>
@@ -3018,7 +3018,7 @@
         <v>3.33</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>29</v>
       </c>
@@ -3092,7 +3092,7 @@
         <v>3.33</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
         <v>29</v>
       </c>
@@ -3166,7 +3166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="38">
         <v>2018</v>
       </c>
@@ -3238,7 +3238,7 @@
         <v>4.83</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="36">
         <v>2017</v>
       </c>
@@ -3310,7 +3310,7 @@
         <v>6.16</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="38">
         <v>2016</v>
       </c>
@@ -3382,7 +3382,7 @@
         <v>3.93</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="36">
         <v>2015</v>
       </c>
@@ -3454,7 +3454,7 @@
         <v>4.79</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="38">
         <v>2014</v>
       </c>
@@ -3526,7 +3526,7 @@
         <v>7.08</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="36">
         <v>2013</v>
       </c>
@@ -3598,7 +3598,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="38" t="s">
         <v>49</v>
       </c>
